--- a/tools/downloads/2026_Performance_Medicine_PM_NEAT_Scoring_Workbook_v0_2.xlsx
+++ b/tools/downloads/2026_Performance_Medicine_PM_NEAT_Scoring_Workbook_v0_2.xlsx
@@ -195,7 +195,7 @@
     <t xml:space="preserve">1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Lifestyle and Preventative Medicine</t>
+    <t xml:space="preserve">Lifestyle and Preventive Medicine</t>
   </si>
   <si>
     <t xml:space="preserve">Health promotion and the prevention of chronic disease: assessment of and intervention on physical activity, diet, sleep, stress, substance use and social connection, and screening for long-term risk; specialist nutrition and sleep provision for performance are scored under 3.2 and 3.6.</t>
